--- a/dist/成果/防治对象/测量表/360421201201114_黄洞村寺门口/沟道纵断面成果表_AFAE900122HF0000ZACS007.xlsx
+++ b/dist/成果/防治对象/测量表/360421201201114_黄洞村寺门口/沟道纵断面成果表_AFAE900122HF0000ZACS007.xlsx
@@ -822,7 +822,7 @@
         <v>28.545</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>29.14559047915797</v>
+        <v>29.00988053710388</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.636529</v>
@@ -850,7 +850,7 @@
         <v>28.327</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>28.86991905846989</v>
+        <v>28.68229827075946</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.63623</v>
@@ -878,7 +878,7 @@
         <v>28.159</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>28.48709959266712</v>
+        <v>28.38981099900381</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.635453</v>
@@ -906,7 +906,7 @@
         <v>27.812</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>28.44973783662455</v>
+        <v>28.23998715613862</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.63469</v>
@@ -990,7 +990,7 @@
         <v>27.129</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>27.3432351142319</v>
+        <v>27.40420288936227</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.633598</v>
@@ -1018,7 +1018,7 @@
         <v>27.067</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>27.15008808114009</v>
+        <v>27.31643013626786</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.633391</v>
@@ -1046,7 +1046,7 @@
         <v>26.823</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>26.90392897460133</v>
+        <v>27.157</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.633312</v>
@@ -1074,7 +1074,7 @@
         <v>26.633</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>26.96058411333384</v>
+        <v>26.79337901917505</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.632825</v>
@@ -1102,7 +1102,7 @@
         <v>26.293</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>26.90927024366946</v>
+        <v>26.69177378628117</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.63255</v>
@@ -1130,7 +1130,7 @@
         <v>26.203</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>26.7132903438143</v>
+        <v>26.47617143037388</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.631808</v>
@@ -1158,7 +1158,7 @@
         <v>25.937</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>26.56743973702505</v>
+        <v>26.11679129692082</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.631306</v>
@@ -1214,7 +1214,7 @@
         <v>24.011</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>24.35183742470744</v>
+        <v>24.4836590892871</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.630348</v>
@@ -1298,7 +1298,7 @@
         <v>22.809</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>23.11000330832509</v>
+        <v>23.17034607111379</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.628926</v>
@@ -1326,7 +1326,7 @@
         <v>22.474</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>22.75150473599229</v>
+        <v>23.15583070630053</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.628243</v>
@@ -1354,7 +1354,7 @@
         <v>22.414</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>22.53576309571525</v>
+        <v>22.99319696320474</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.628073</v>
@@ -1382,7 +1382,7 @@
         <v>22.32</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>22.45569983515831</v>
+        <v>22.54077627788814</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>115.628011</v>
@@ -1410,7 +1410,7 @@
         <v>22.185</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>22.41164280982983</v>
+        <v>22.33073319933683</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>115.627839</v>
@@ -1438,7 +1438,7 @@
         <v>21.65</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>21.9408594245007</v>
+        <v>21.89701320270228</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>115.627696</v>
@@ -1466,7 +1466,7 @@
         <v>21.212</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>21.70878459466482</v>
+        <v>21.66005358273982</v>
       </c>
       <c r="G35" s="23" t="n">
         <v>115.627446</v>
@@ -1494,7 +1494,7 @@
         <v>21.161</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>21.34134756996229</v>
+        <v>21.36687126765582</v>
       </c>
       <c r="G36" s="23" t="n">
         <v>115.627339</v>
@@ -1522,7 +1522,7 @@
         <v>20.956</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>21.16855770083923</v>
+        <v>21.1899227314318</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>115.627298</v>
@@ -1550,7 +1550,7 @@
         <v>20.875</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>21.12731130287329</v>
+        <v>21.10914103445444</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>115.627119</v>
@@ -1574,16 +1574,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
